--- a/outputs/Block2_2026_Fold_Targets_v12.xlsx
+++ b/outputs/Block2_2026_Fold_Targets_v12.xlsx
@@ -588,7 +588,7 @@
         <v>57</v>
       </c>
       <c r="F2">
-        <v>0.5099509392265194</v>
+        <v>0.5213255079006773</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -608,7 +608,7 @@
         <v>57</v>
       </c>
       <c r="F3">
-        <v>0.4620490607734807</v>
+        <v>0.4506744920993228</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -628,7 +628,7 @@
         <v>57</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -648,7 +648,7 @@
         <v>57</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -668,7 +668,7 @@
         <v>57</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -688,7 +688,7 @@
         <v>57</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -748,7 +748,7 @@
         <v>57</v>
       </c>
       <c r="F10">
-        <v>186</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -788,7 +788,7 @@
         <v>57</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -808,7 +808,7 @@
         <v>57</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -828,7 +828,7 @@
         <v>57</v>
       </c>
       <c r="F14">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -848,7 +848,7 @@
         <v>57</v>
       </c>
       <c r="F15">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -868,7 +868,7 @@
         <v>57</v>
       </c>
       <c r="F16">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -888,7 +888,7 @@
         <v>57</v>
       </c>
       <c r="F17">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -908,7 +908,7 @@
         <v>57</v>
       </c>
       <c r="F18">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1168,7 +1168,7 @@
         <v>57</v>
       </c>
       <c r="F31">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -1228,7 +1228,7 @@
         <v>57</v>
       </c>
       <c r="F34">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -1288,7 +1288,7 @@
         <v>58</v>
       </c>
       <c r="F37">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -1308,7 +1308,7 @@
         <v>58</v>
       </c>
       <c r="F38">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -1328,7 +1328,7 @@
         <v>58</v>
       </c>
       <c r="F39">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -1348,7 +1348,7 @@
         <v>58</v>
       </c>
       <c r="F40">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -1368,7 +1368,7 @@
         <v>58</v>
       </c>
       <c r="F41">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -1388,7 +1388,7 @@
         <v>58</v>
       </c>
       <c r="F42">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -1408,7 +1408,7 @@
         <v>58</v>
       </c>
       <c r="F43">
-        <v>212</v>
+        <v>218</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -1428,7 +1428,7 @@
         <v>57</v>
       </c>
       <c r="F44">
-        <v>0.5099509392265194</v>
+        <v>0.5213255079006772</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -1448,7 +1448,7 @@
         <v>57</v>
       </c>
       <c r="F45">
-        <v>0.4620490607734807</v>
+        <v>0.4506744920993228</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -1508,7 +1508,7 @@
         <v>57</v>
       </c>
       <c r="F48">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -1528,7 +1528,7 @@
         <v>57</v>
       </c>
       <c r="F49">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -1548,7 +1548,7 @@
         <v>57</v>
       </c>
       <c r="F50">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -1588,7 +1588,7 @@
         <v>57</v>
       </c>
       <c r="F52">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -1668,7 +1668,7 @@
         <v>57</v>
       </c>
       <c r="F56">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -1688,7 +1688,7 @@
         <v>57</v>
       </c>
       <c r="F57">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -1708,7 +1708,7 @@
         <v>57</v>
       </c>
       <c r="F58">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -1728,7 +1728,7 @@
         <v>57</v>
       </c>
       <c r="F59">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -1748,7 +1748,7 @@
         <v>57</v>
       </c>
       <c r="F60">
-        <v>175</v>
+        <v>184</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -1768,7 +1768,7 @@
         <v>57</v>
       </c>
       <c r="F61">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -1908,7 +1908,7 @@
         <v>57</v>
       </c>
       <c r="F68">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -1928,7 +1928,7 @@
         <v>57</v>
       </c>
       <c r="F69">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -1948,7 +1948,7 @@
         <v>57</v>
       </c>
       <c r="F70">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -2068,7 +2068,7 @@
         <v>57</v>
       </c>
       <c r="F76">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -2108,7 +2108,7 @@
         <v>58</v>
       </c>
       <c r="F78">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -2148,7 +2148,7 @@
         <v>58</v>
       </c>
       <c r="F80">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -2168,7 +2168,7 @@
         <v>58</v>
       </c>
       <c r="F81">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -2188,7 +2188,7 @@
         <v>58</v>
       </c>
       <c r="F82">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -2208,7 +2208,7 @@
         <v>58</v>
       </c>
       <c r="F83">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -2228,7 +2228,7 @@
         <v>58</v>
       </c>
       <c r="F84">
-        <v>216</v>
+        <v>209</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -2248,7 +2248,7 @@
         <v>58</v>
       </c>
       <c r="F85">
-        <v>219</v>
+        <v>226</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -2268,7 +2268,7 @@
         <v>57</v>
       </c>
       <c r="F86">
-        <v>0.5098197790055249</v>
+        <v>0.5211914221218962</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -2288,7 +2288,7 @@
         <v>57</v>
       </c>
       <c r="F87">
-        <v>0.4619302209944752</v>
+        <v>0.4505585778781038</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -2308,7 +2308,7 @@
         <v>57</v>
       </c>
       <c r="F88">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -2348,7 +2348,7 @@
         <v>57</v>
       </c>
       <c r="F90">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -2368,7 +2368,7 @@
         <v>57</v>
       </c>
       <c r="F91">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -2388,7 +2388,7 @@
         <v>57</v>
       </c>
       <c r="F92">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -2408,7 +2408,7 @@
         <v>57</v>
       </c>
       <c r="F93">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -2428,7 +2428,7 @@
         <v>57</v>
       </c>
       <c r="F94">
-        <v>178</v>
+        <v>184</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -2488,7 +2488,7 @@
         <v>57</v>
       </c>
       <c r="F97">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98" spans="1:6">
@@ -2528,7 +2528,7 @@
         <v>57</v>
       </c>
       <c r="F99">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -2568,7 +2568,7 @@
         <v>57</v>
       </c>
       <c r="F101">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -2588,7 +2588,7 @@
         <v>57</v>
       </c>
       <c r="F102">
-        <v>167</v>
+        <v>159</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -2608,7 +2608,7 @@
         <v>57</v>
       </c>
       <c r="F103">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="104" spans="1:6">
@@ -2628,7 +2628,7 @@
         <v>57</v>
       </c>
       <c r="F104">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -2708,7 +2708,7 @@
         <v>57</v>
       </c>
       <c r="F108">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109" spans="1:6">
@@ -2888,7 +2888,7 @@
         <v>57</v>
       </c>
       <c r="F117">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -2908,7 +2908,7 @@
         <v>57</v>
       </c>
       <c r="F118">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="119" spans="1:6">
@@ -2968,7 +2968,7 @@
         <v>58</v>
       </c>
       <c r="F121">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -2988,7 +2988,7 @@
         <v>58</v>
       </c>
       <c r="F122">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -3008,7 +3008,7 @@
         <v>58</v>
       </c>
       <c r="F123">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -3028,7 +3028,7 @@
         <v>58</v>
       </c>
       <c r="F124">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -3048,7 +3048,7 @@
         <v>58</v>
       </c>
       <c r="F125">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -3068,7 +3068,7 @@
         <v>58</v>
       </c>
       <c r="F126">
-        <v>224</v>
+        <v>233</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -3088,7 +3088,7 @@
         <v>58</v>
       </c>
       <c r="F127">
-        <v>211</v>
+        <v>202</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -3108,7 +3108,7 @@
         <v>57</v>
       </c>
       <c r="F128">
-        <v>0.5078523756906078</v>
+        <v>0.5191801354401807</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -3128,7 +3128,7 @@
         <v>57</v>
       </c>
       <c r="F129">
-        <v>0.4601476243093923</v>
+        <v>0.4488198645598194</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -3248,7 +3248,7 @@
         <v>57</v>
       </c>
       <c r="F135">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -3268,7 +3268,7 @@
         <v>57</v>
       </c>
       <c r="F136">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -3288,7 +3288,7 @@
         <v>57</v>
       </c>
       <c r="F137">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -3628,7 +3628,7 @@
         <v>57</v>
       </c>
       <c r="F154">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -3768,7 +3768,7 @@
         <v>57</v>
       </c>
       <c r="F161">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162" spans="1:6">
@@ -3808,7 +3808,7 @@
         <v>58</v>
       </c>
       <c r="F163">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -3828,7 +3828,7 @@
         <v>58</v>
       </c>
       <c r="F164">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="165" spans="1:6">
@@ -3868,7 +3868,7 @@
         <v>58</v>
       </c>
       <c r="F166">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="167" spans="1:6">
@@ -3888,7 +3888,7 @@
         <v>58</v>
       </c>
       <c r="F167">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -3908,7 +3908,7 @@
         <v>58</v>
       </c>
       <c r="F168">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="169" spans="1:6">
@@ -3928,7 +3928,7 @@
         <v>58</v>
       </c>
       <c r="F169">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="170" spans="1:6">
@@ -3948,7 +3948,7 @@
         <v>57</v>
       </c>
       <c r="F170">
-        <v>0.509032817679558</v>
+        <v>0.52038690744921</v>
       </c>
     </row>
     <row r="171" spans="1:6">
@@ -3968,7 +3968,7 @@
         <v>57</v>
       </c>
       <c r="F171">
-        <v>0.461217182320442</v>
+        <v>0.44986309255079</v>
       </c>
     </row>
     <row r="172" spans="1:6">
@@ -3988,7 +3988,7 @@
         <v>57</v>
       </c>
       <c r="F172">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173" spans="1:6">
@@ -4008,7 +4008,7 @@
         <v>57</v>
       </c>
       <c r="F173">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174" spans="1:6">
@@ -4028,7 +4028,7 @@
         <v>57</v>
       </c>
       <c r="F174">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="175" spans="1:6">
@@ -4048,7 +4048,7 @@
         <v>57</v>
       </c>
       <c r="F175">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="176" spans="1:6">
@@ -4068,7 +4068,7 @@
         <v>57</v>
       </c>
       <c r="F176">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="177" spans="1:6">
@@ -4088,7 +4088,7 @@
         <v>57</v>
       </c>
       <c r="F177">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="178" spans="1:6">
@@ -4108,7 +4108,7 @@
         <v>57</v>
       </c>
       <c r="F178">
-        <v>189</v>
+        <v>175</v>
       </c>
     </row>
     <row r="179" spans="1:6">
@@ -4128,7 +4128,7 @@
         <v>57</v>
       </c>
       <c r="F179">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="180" spans="1:6">
@@ -4208,7 +4208,7 @@
         <v>57</v>
       </c>
       <c r="F183">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="184" spans="1:6">
@@ -4228,7 +4228,7 @@
         <v>57</v>
       </c>
       <c r="F184">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="185" spans="1:6">
@@ -4248,7 +4248,7 @@
         <v>57</v>
       </c>
       <c r="F185">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="186" spans="1:6">
@@ -4268,7 +4268,7 @@
         <v>57</v>
       </c>
       <c r="F186">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="187" spans="1:6">
@@ -4348,7 +4348,7 @@
         <v>57</v>
       </c>
       <c r="F190">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191" spans="1:6">
@@ -4408,7 +4408,7 @@
         <v>57</v>
       </c>
       <c r="F193">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194" spans="1:6">
@@ -4548,7 +4548,7 @@
         <v>57</v>
       </c>
       <c r="F200">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201" spans="1:6">
@@ -4588,7 +4588,7 @@
         <v>57</v>
       </c>
       <c r="F202">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="203" spans="1:6">
@@ -4628,7 +4628,7 @@
         <v>58</v>
       </c>
       <c r="F204">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="205" spans="1:6">
@@ -4668,7 +4668,7 @@
         <v>58</v>
       </c>
       <c r="F206">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="207" spans="1:6">
@@ -4688,7 +4688,7 @@
         <v>58</v>
       </c>
       <c r="F207">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="208" spans="1:6">
@@ -4708,7 +4708,7 @@
         <v>58</v>
       </c>
       <c r="F208">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="209" spans="1:6">
@@ -4728,7 +4728,7 @@
         <v>58</v>
       </c>
       <c r="F209">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="210" spans="1:6">
@@ -4748,7 +4748,7 @@
         <v>58</v>
       </c>
       <c r="F210">
-        <v>231</v>
+        <v>219</v>
       </c>
     </row>
     <row r="211" spans="1:6">
@@ -4768,7 +4768,7 @@
         <v>58</v>
       </c>
       <c r="F211">
-        <v>204</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>
